--- a/光伏配储项目/电价数据/2026/廊田站.xlsx
+++ b/光伏配储项目/电价数据/2026/廊田站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5125599999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.85068</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.67914</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58445</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51449</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.60881</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.51193</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03785</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04015999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03724</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03348</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03546</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02292</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02563</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02474</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01802</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01324</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.02709</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.03979</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03775999999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.007820000000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20024</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55628</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.67852</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.56909</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5660700000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79883</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6272799999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63149</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73898</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9295099999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65964</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58331</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7231000000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62393</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.50048</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69178</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6366499999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.54588</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.66584</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49346</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48427</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55152</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.48973</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24601</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18956</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.17459</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.11017</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23536</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.16356</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.0399</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.02852</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.13585</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.19716</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.18477</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.02062</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04199</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03589</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.43567</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.45213</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.58499</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48379</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.58787</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.53274</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67155</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63217</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71941</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76573</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47145</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46287</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44247</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50984</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43953</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26133</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25996</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25283</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20899</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.47302</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.50815</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46308</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.52559</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5256000000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60885</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.57743</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59613</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46386</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48221</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43645</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41984</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47787</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12483</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24127</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19814</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28231</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20117</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56023</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.22807</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16939</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.10994</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02203</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.03503</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02595</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10201</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19405</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.1945</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10229</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10144</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10215</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16453</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3161</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.21474</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.22372</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.21554</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20973</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04474</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.22057</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21661</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19472</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02873</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.18223</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09625</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03292</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0335</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03558</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03767</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03513</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04227</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03824</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04607</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.03756</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05797</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.01042</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03405</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09595000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35076</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21007</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05118</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.01952</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33528</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31699</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9140900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86252</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29602</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88715</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18674</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86848</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53573</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3305</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03267</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53043</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79069</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52955</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77267</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7773</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87674</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87371</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49287</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39953</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20663</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62149</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53823</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49759</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43708</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58538</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42699</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59556</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60114</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6900499999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58013</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.45999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85949</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.7908500000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.80098</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44035</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5466</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45158</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46355</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16622</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19287</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.09934999999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44279</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59497</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88964</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45594</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16047</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69978</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6641900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57884</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44014</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50018</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42313</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55062</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15659</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01034</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25526</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56976</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46196</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8464700000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46419</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43619</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32328</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22556</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15281</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01131</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00945</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13616</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24729</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13669</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.18403</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.04355</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.00383</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.02054</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10784</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10741</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12635</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13583</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14072</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45117</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44263</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34815</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53692</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.18031</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.16436</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20073</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18162</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.04911</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24222</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25966</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35983</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42569</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24944</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.21254</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.68984</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50987</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22207</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31541</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.18434</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.21894</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.17791</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.21361</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.23994</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.24059</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.23965</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34947</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.21612</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.08438</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.07801000000000001</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.08154</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.08508</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.05912</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.05656</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.08309</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.08248999999999999</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.08415</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.02721</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.08389000000000001</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.08658</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.08356999999999999</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.08635</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65638</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76966</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45166</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45736</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3442</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.07573000000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.06895</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.06931</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21643</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.23055</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6395</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59711</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60476</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8098500000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.81189</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44189</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48908</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47026</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35981</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52686</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47942</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48216</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.10545</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44666</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.17672</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.07449</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.08993000000000001</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.09954</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.11763</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.06289</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.22277</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.23227</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.09368000000000001</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.00558</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.04795</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.09165999999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.02813</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.11372</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.03284</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.03743</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.02824</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.02635</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.01888</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.05192</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.24687</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.24845</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.24638</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49184</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50112</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5045500000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.68991</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7110700000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.91973</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5269299999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8059500000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5821900000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52489</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8311799999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7701399999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234400000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67215</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47164</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48162</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47606</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46883</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55108</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45496</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45386</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.28637</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.08798</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.03065</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.11242</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.06573000000000001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04541</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.04998</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.03892</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.03614</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.0751</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.08594</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.05754</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.04184</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01876</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.08072</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.07897</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.10883</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.09440000000000001</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.24295</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.25371</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40869</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36504</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25752</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22562</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.26307</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22987</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23033</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13937</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.23871</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.23457</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16937</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.24133</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23384</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23857</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.21435</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.04065999999999999</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.20728</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.21578</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.19488</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.23367</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.23899</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.19756</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.24136</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.24172</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3407</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.13897</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22719</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.22423</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.26667</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26748</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.26086</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.63109</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.76383</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75422</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.58108</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02587</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.20189</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.20109</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02456</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04199</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04189</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.00461</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.20988</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20966</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18151</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.19356</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18859</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16193</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.23686</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32152</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.16525</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5198700000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5310499999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.26828</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.21464</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.10057</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.12783</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.08423</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.09107999999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.2488</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14176</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.21775</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.23662</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.24362</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34004</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8227899999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.53699</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.25061</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.24361</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.22656</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.07568999999999999</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.09645999999999999</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.08992</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.06626</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.09548000000000001</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.21721</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.21916</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.09498000000000001</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.09619</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.09512000000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.09673999999999999</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.21127</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.26296</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46874</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.45269</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27459</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33629</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.21504</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.10246</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.25746</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.25747</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.21513</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.24684</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.25107</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.08331000000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.22292</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.07793000000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.10811</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.10367</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.10408</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.24713</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.08717</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.07894</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.09395000000000001</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.08575000000000001</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.22442</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25921</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.25252</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.10583</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.22906</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.42622</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.44773</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.45519</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7445499999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34279</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.23429</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.08688</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.23983</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.23908</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.24858</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.24492</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.08059999999999999</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.09597</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.24163</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.22272</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.07511</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21568</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.23971</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.06052</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.10807</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.05640999999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.02869</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01865</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03666</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.00191</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03088</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.04126</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.23011</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08738</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.05222</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.04107</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.09551999999999999</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.10279</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.09917000000000001</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.26281</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.11163</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.11915</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.23229</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.22103</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24845</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.24849</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.24338</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.24355</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.56404</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45991</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.24112</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.24564</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.23937</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.24156</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.09337000000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.10067</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25633</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22469</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>-0.03132</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>-0.03552</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.12012</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.05665</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.08222</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.00553</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.0464</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.06992</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.01075</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.11829</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.00091</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26118</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.26493</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3339</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.08746</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.24316</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.21534</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.24131</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.24141</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.07282</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.04664</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.02242</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00396</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.03251</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.00436</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.15307</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.02644</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.04884</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.04449</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>-0.04868</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.04847</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23976</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24192</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.24255</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47466</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37727</v>
       </c>
     </row>
   </sheetData>
